--- a/results/job_matches_2026-06-20.xlsx
+++ b/results/job_matches_2026-06-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer- Investment Research and Data</t>
+          <t>Data Engineer C1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,69 +556,69 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f71b2d395389103</t>
+          <t>https://www.indeed.com/viewjob?jk=bd7a10fab4aead6b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior IT Big Data Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, API Gateway, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c248fdc62311341</t>
+          <t>https://www.indeed.com/viewjob?jk=6a6a3f2e51311a48</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior IT Big Data Developer</t>
+          <t>Sr. Associate, Site Reliability Engineering</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,42 +626,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, Lambda, Athena, S3, API Gateway, ECS, IAM, RDS, Azure, Databricks</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a6a3f2e51311a48</t>
+          <t>https://www.indeed.com/viewjob?jk=1d58654d97d98c4a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Associate, Site Reliability Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, API Gateway, ECS, IAM, RDS, Azure, Databricks</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d58654d97d98c4a</t>
+          <t>https://www.indeed.com/viewjob?jk=60c093da65d37212</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, Glue, Lambda, Step Functions, API Gateway, RDS, Oracle, MySQL, DynamoDB, Splunk</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,662 +706,662 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60c093da65d37212</t>
+          <t>https://www.indeed.com/viewjob?jk=f2637106dd2c7c5c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Consultant — System Integration &amp; MDM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Triade Flevoland</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, API Gateway, RDS, Oracle, MySQL, DynamoDB, Splunk</t>
+          <t>AWS, Glue, ECS, RDS, Azure, Databricks, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2637106dd2c7c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=d22f323af4989133</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Sr. Feature Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bertrandt</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, PostgreSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=261057ab4b84e0de</t>
+          <t>https://www.indeed.com/viewjob?jk=b8442abf91777c1a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Engineer - SFL Scientific</t>
+          <t>Data Engineer/Database Administrator_ (Only W2)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Chuwa America</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b09c16289d91a9c2</t>
+          <t>https://www.indeed.com/viewjob?jk=adac783343467c24</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Engineer - SFL Scientific</t>
+          <t>Senior Analytics Engineer (Data + BI) — Healthcare</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>EMR, Redshift, RDS, Databricks, BigQuery, Snowflake, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36c5a207a5141493</t>
+          <t>https://www.indeed.com/viewjob?jk=e342cff8300db11b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Engineer - SFL Scientific</t>
+          <t>Database Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Magnaflow</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Oceanside, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, SQL Server, MySQL, NoSQL, Snowflake Schema</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75337eae4d7f1ca4</t>
+          <t>https://www.indeed.com/viewjob?jk=3505e51fdb71a895</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Engineer - SFL Scientific</t>
+          <t>Senior Software Engineer - Information Products Team</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Wellmark Blue Cross and Blue Shield</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>13.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Azure, Spark, PySpark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3778a847e69710fd</t>
+          <t>https://www.indeed.com/viewjob?jk=59625199b42cb5da</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Engineer - SFL Scientific</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>13.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ce419a88fc032ba</t>
+          <t>https://www.indeed.com/viewjob?jk=d6a583130162de58</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Engineer - SFL Scientific</t>
+          <t>Software Production Support Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>IntelliLink Technologies</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>13.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2228b29878769f7c</t>
+          <t>https://www.indeed.com/viewjob?jk=416511572a3a38ba</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Engineer - SFL Scientific</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Arc Technologies Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>12.5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d37d79e2a41923a0</t>
+          <t>https://www.indeed.com/viewjob?jk=af690b2327755c54</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI Engineer - SFL Scientific</t>
+          <t>Data Engineer (SMTS / LMTS) - MDM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>12.5</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58947e3b3990b58a</t>
+          <t>https://www.indeed.com/viewjob?jk=50844673569c1fb8</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI Engineer - SFL Scientific</t>
+          <t>Full Stack Developer -In office, Alpharetta, GA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>12.5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74d31ddfd51c98d4</t>
+          <t>https://www.indeed.com/viewjob?jk=789775eb6e130995</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI Engineer - SFL Scientific</t>
+          <t>Digital Provider Software Development Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>12.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be3fa46940f05bde</t>
+          <t>https://www.indeed.com/viewjob?jk=c8e58013e22bddb4</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI Engineer - SFL Scientific</t>
+          <t>Backend Java Software Engineer III</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96ba9f5e4d52822c</t>
+          <t>https://www.indeed.com/viewjob?jk=9251732e66580bb6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI Engineer - SFL Scientific</t>
+          <t>Senior Software Engineer - LSP</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>project44</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2c36b54a1aabffc</t>
+          <t>https://www.indeed.com/viewjob?jk=d185ef3015154b1f</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI Engineer - SFL Scientific</t>
+          <t>Senior Software Engineer - LSP</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Convey</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07707c89f2c2beaf</t>
+          <t>https://www.indeed.com/viewjob?jk=46e5e7f505da6aea</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI Engineer - SFL Scientific</t>
+          <t>Jr. Feature Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>11.8</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2773697f2a464bd</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3a9fd6adbb852f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI Engineer - SFL Scientific</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.3</v>
+        <v>11.8</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aca527a7ca4ae8cc</t>
+          <t>https://www.indeed.com/viewjob?jk=372d6a67c10b163b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI Engineer - SFL Scientific</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>APLOMB Technologies</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.3</v>
+        <v>11.8</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0668436ba0d957fa</t>
+          <t>https://www.indeed.com/viewjob?jk=45738cf915b51235</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AI Engineer - SFL Scientific</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15.3</v>
+        <v>11.8</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,172 +1371,172 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56e75a9810e146b9</t>
+          <t>https://www.indeed.com/viewjob?jk=a2b31f13d8496041</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AI Engineer - SFL Scientific</t>
+          <t>Fabric Platform Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>15.3</v>
+        <v>11.8</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e376f34a2464492</t>
+          <t>https://www.indeed.com/viewjob?jk=3c7b8660e24dfc38</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AI Engineer - SFL Scientific</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Lake Forest, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>15.3</v>
+        <v>11.8</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b599a8fb3b53dca2</t>
+          <t>https://www.indeed.com/viewjob?jk=da3c07885d8b3693</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI Engineer - SFL Scientific</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Marysville, OH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>15.3</v>
+        <v>11.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0666b2ee03b1b4ed</t>
+          <t>https://www.indeed.com/viewjob?jk=c9c434dda73e4155</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AI Engineer - SFL Scientific</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>UDR</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>15.3</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=210574454b039b8d</t>
+          <t>https://www.indeed.com/viewjob?jk=1fb77bd035c0b222</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AI Engineer - SFL Scientific</t>
+          <t>Sr Snowflake/DWH/ETL Informatica Consultant</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Hermitage Info Tech Llc</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>15.3</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>RDS, Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01334b7e21714bf3</t>
+          <t>https://www.indeed.com/viewjob?jk=bb7813160ee888e4</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AI Engineer - SFL Scientific</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Blackhawk Network</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>15.3</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,137 +1581,137 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5758da877fbc35e</t>
+          <t>https://www.indeed.com/viewjob?jk=b3ee41a8c52420bf</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AI Engineer - SFL Scientific</t>
+          <t>Senior Software Development Engineer (Site Reliability)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>15.3</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b88cc808352c6ed</t>
+          <t>https://www.indeed.com/viewjob?jk=56047e794a998d7c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AI Engineer - SFL Scientific</t>
+          <t>Senior Software Development Engineer (Site Reliability)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Northbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>15.3</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e98cca52bbe68424</t>
+          <t>https://www.indeed.com/viewjob?jk=728e137e29293bde</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AI Engineer - SFL Scientific</t>
+          <t>Senior Software Development Engineer (Site Reliability)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>15.3</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2e0cd792417383</t>
+          <t>https://www.indeed.com/viewjob?jk=297ddc2108f979e1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AI Engineer - SFL Scientific</t>
+          <t>Data Engineer 3 - Reston, VA - Freewheel</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>15.3</v>
+        <v>11.1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Snowflake, ETL, dbt, Kubernetes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,137 +1721,137 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9920b9b0db4e2308</t>
+          <t>https://www.indeed.com/viewjob?jk=24d54b28b92ef5c9</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AI Engineer - SFL Scientific</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>RAZR Marketing, Inc.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>15.3</v>
+        <v>11.1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, PostgreSQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94af0e0a513dab44</t>
+          <t>https://www.indeed.com/viewjob?jk=7fde30b21f3e7647</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AI Engineer - SFL Scientific</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Intellisoft Technologies</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>15.3</v>
+        <v>11.1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9da85b011f3c9bb7</t>
+          <t>https://www.indeed.com/viewjob?jk=8c473d3620c861ac</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AI Engineer - SFL Scientific</t>
+          <t>Platform Engineer SOW198 Datahub Platform</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>15.3</v>
+        <v>11.1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f747e8cd9f65503</t>
+          <t>https://www.indeed.com/viewjob?jk=0fab0a2c9cd2208f</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AI Engineer - SFL Scientific</t>
+          <t>DevFinOps Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>15.3</v>
+        <v>11.1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,277 +1861,277 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e6716e1346a404f</t>
+          <t>https://www.indeed.com/viewjob?jk=84a584e2ae5c7382</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AI Engineer - SFL Scientific</t>
+          <t>Senior Associate - Enterprise Intelligence Analytics Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>15.3</v>
+        <v>11.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f32c63274ea61adf</t>
+          <t>https://www.indeed.com/viewjob?jk=f738fb7e1c97b094</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AI Engineer - SFL Scientific</t>
+          <t>Senior Associate - Senior Associate, Analytics Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>15.3</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>RDS, Databricks, BigQuery, Scala, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, Git</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed88553db5377339</t>
+          <t>https://www.indeed.com/viewjob?jk=6e6fe876bea05203</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AI Engineer - SFL Scientific</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Molex</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Lisle, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>15.3</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, Glue, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc602142c0dc423a</t>
+          <t>https://www.indeed.com/viewjob?jk=461471cb36992ab7</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AI Engineer - SFL Scientific</t>
+          <t>Associate</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>15.3</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>RDS, Azure, Hadoop, Hive, Spark, PySpark, Kafka, Snowflake, ETL, Splunk</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69d3c14f109508ef</t>
+          <t>https://www.indeed.com/viewjob?jk=54b42443ee3c4437</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AI Engineer - SFL Scientific</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>15.3</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29431c61744eb526</t>
+          <t>https://www.indeed.com/viewjob?jk=bc4bd1d0f1519ea1</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Consultant — System Integration &amp; MDM</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Triade Flevoland</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>15.3</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, ECS, RDS, Azure, Databricks, GCP, Spark, Kafka, Snowflake</t>
+          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d22f323af4989133</t>
+          <t>https://www.indeed.com/viewjob?jk=cf3f2dbb3812e475</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ML Engineer ((GCP) – Finance Data &amp; AI Platform)</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BizTech Fusion</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>15.3</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala</t>
+          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08ee595f70e46b33</t>
+          <t>https://www.indeed.com/viewjob?jk=eeb8ab90439d98b8</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer/Database Administrator_ (Only W2)</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Chuwa America</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>14.6</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala, PostgreSQL</t>
+          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adac783343467c24</t>
+          <t>https://www.indeed.com/viewjob?jk=ea6ecf773d8deb21</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (Data + BI) — Healthcare</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Kearney, NE, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>EMR, Redshift, RDS, Databricks, BigQuery, Snowflake, ELT, dbt, Power BI, Tableau</t>
+          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,67 +2176,67 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e342cff8300db11b</t>
+          <t>https://www.indeed.com/viewjob?jk=a1d8f5634d6f6d76</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer - FinOps</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Grand Island, NE, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, ECS, RDS, Azure, Spark</t>
+          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6922cd9384b21595</t>
+          <t>https://www.indeed.com/viewjob?jk=2ccaa9de6cb6d799</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Database Developer</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Magnaflow</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Oceanside, CA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, SQL Server, MySQL, NoSQL, Snowflake Schema</t>
+          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3505e51fdb71a895</t>
+          <t>https://www.indeed.com/viewjob?jk=47d6b37f8d80d085</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Power Automate - Contract</t>
+          <t>Data Engineer, Cat Digital Data &amp; AI</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>hr@brxio.com</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02612783f72a36f6</t>
+          <t>https://www.indeed.com/viewjob?jk=826181dbe0e126ae</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Information Products Team</t>
+          <t>IT Data Solutions Developer - Intermediate</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Wellmark Blue Cross and Blue Shield</t>
+          <t>Atrium Health</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Azure, Spark, PySpark</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,67 +2316,67 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59625199b42cb5da</t>
+          <t>https://www.indeed.com/viewjob?jk=9c5097ade3e79b6c</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6311a108ad80bb92</t>
+          <t>https://www.indeed.com/viewjob?jk=02fed8f682ea9929</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Software Engineer - AI Innovation Team</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, Data Modeling, ETL, ELT, Talend</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,67 +2386,67 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6a583130162de58</t>
+          <t>https://www.indeed.com/viewjob?jk=893eebcde0f6a410</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Senior Software Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22024abdb3ab3a83</t>
+          <t>https://www.indeed.com/viewjob?jk=4c67eab5c67331a9</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer (SMTS / LMTS) - MDM</t>
+          <t>Product Software Engineer I</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, Kinesis, Databricks, Spark, Scala, Kafka, Snowflake, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,67 +2456,67 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50844673569c1fb8</t>
+          <t>https://www.indeed.com/viewjob?jk=9c5d705afdfcef3f</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>E Source</t>
+          <t>Blue Learning</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, PostgreSQL, ETL, Jenkins, Docker, Jenkins</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, ETL, ELT, dbt, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cf3a91683e2fbee</t>
+          <t>https://www.indeed.com/viewjob?jk=1e8db13fab29835e</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Full Stack Developer -In office, Alpharetta, GA</t>
+          <t>Senior Cloud Solutions Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>loanDepot</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=789775eb6e130995</t>
+          <t>https://www.indeed.com/viewjob?jk=275de5114fc3f721</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LSP</t>
+          <t>Shopify Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>project44</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, S3, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d185ef3015154b1f</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc5601c059bd73a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LSP</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Convey</t>
+          <t>GCON Inc</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46e5e7f505da6aea</t>
+          <t>https://www.indeed.com/viewjob?jk=d9b57204f314618a</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Digital Provider Software Development Engineer</t>
+          <t>Integration Developer - (8+ years w Java/Spring Boot Framework)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Cloud and Things</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2630,1091 +2630,6 @@
         </is>
       </c>
       <c r="G63" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c8e58013e22bddb4</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Backend Java Software Engineer III</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9251732e66580bb6</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Full Stack Developer -In office, Alpharetta, GA</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Global Payments</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Alpharetta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c9260b2578b52c9d</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>E Source</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>AWS, Scala, MongoDB, Cassandra, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3ab1bd8dcae6ad9c</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>EXL Service</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Scala, Snowflake</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=372d6a67c10b163b</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>APLOMB Technologies</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=45738cf915b51235</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Adobe</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, ELT, dbt, Tableau</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a2b31f13d8496041</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Mountain View, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>AWS, Google Cloud Platform, GCP, Dataflow, Hadoop, Hive, HBase, Oozie, Spark, PySpark</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=690e477dea973841</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Data Engineer III</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Grainger</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Lake Forest, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=da3c07885d8b3693</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>LTIMindtree</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Marysville, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c9c434dda73e4155</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Senior Data Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>UDR</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Highlands Ranch, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1fb77bd035c0b222</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Sr Snowflake/DWH/ETL Informatica Consultant</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Hermitage Info Tech Llc</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ETL</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bb7813160ee888e4</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Blackhawk Network</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Pleasanton, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b3ee41a8c52420bf</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Senior Software Development Engineer (Site Reliability)</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Scottsdale, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=56047e794a998d7c</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Senior Software Development Engineer (Site Reliability)</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Northbrook, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=728e137e29293bde</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Senior Software Development Engineer (Site Reliability)</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Richardson, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=297ddc2108f979e1</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Associate, Software Engineer, Applications</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>BlackRock</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>API Gateway, RDS, Azure, Scala, Kafka, Oracle, MySQL, Splunk, CI/CD, Maven</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=956dc941dad64afb</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Mid Level Software Engineer</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Sunwest Bank</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Sandy, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f3fc340c895d6105</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Data Engineer 3 - Reston, VA - Freewheel</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Comcast</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Reston, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Snowflake, ETL, dbt, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24d54b28b92ef5c9</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Intellisoft Technologies</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Bentonville, AR, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8c473d3620c861ac</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Platform Engineer SOW198 Datahub Platform</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0fab0a2c9cd2208f</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>DevFinOps Engineer</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>JLL</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=84a584e2ae5c7382</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Senior Associate - Enterprise Intelligence Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>New York Life</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, dbt, Power BI</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f738fb7e1c97b094</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Senior Associate - Senior Associate, Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>New York Life</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, BigQuery, Scala, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6e6fe876bea05203</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer - AI Innovation Team</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>BECU</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>WA, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=893eebcde0f6a410</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Roadrunner</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Downers Grove, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=02fed8f682ea9929</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Software Engineer, Fullstack and Developer Experience</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bea3e6c2fbbe5741</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Product Software Engineer I</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Glendale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, Databricks, Spark, Scala, Kafka, Snowflake, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9c5d705afdfcef3f</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Blue Learning</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Lewisville, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, ETL, ELT, dbt, Tableau, Airflow</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1e8db13fab29835e</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Waystar</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Splunk, CI/CD, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5e379b3e4a12afd8</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>BI Developer</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>GCON Inc</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau, Airflow</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d9b57204f314618a</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Integration Developer - (8+ years w Java/Spring Boot Framework)</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Cloud and Things</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Brooklyn, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Git</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=6ef55b38d756ce85</t>
         </is>

--- a/results/job_matches_2026-06-20.xlsx
+++ b/results/job_matches_2026-06-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,35 +468,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr. Developer</t>
+          <t>Senior Databricks Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25.7</v>
+        <v>18.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a73d712d100166c</t>
+          <t>https://www.indeed.com/viewjob?jk=f289865d551fa1a3</t>
         </is>
       </c>
     </row>
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (Data + BI) — Healthcare</t>
+          <t>Senior Snowflake Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,17 +836,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>EMR, Redshift, RDS, Databricks, BigQuery, Snowflake, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e342cff8300db11b</t>
+          <t>https://www.indeed.com/viewjob?jk=cf016976f76e7f0a</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Backend Java Software Engineer III</t>
+          <t>Senior Software Engineer - LSP</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>project44</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9251732e66580bb6</t>
+          <t>https://www.indeed.com/viewjob?jk=d185ef3015154b1f</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>project44</t>
+          <t>Convey</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d185ef3015154b1f</t>
+          <t>https://www.indeed.com/viewjob?jk=46e5e7f505da6aea</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LSP</t>
+          <t>Jr. Feature Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Convey</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46e5e7f505da6aea</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3a9fd6adbb852f</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Jr. Feature Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3a9fd6adbb852f</t>
+          <t>https://www.indeed.com/viewjob?jk=372d6a67c10b163b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>APLOMB Technologies</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372d6a67c10b163b</t>
+          <t>https://www.indeed.com/viewjob?jk=45738cf915b51235</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Fabric Platform Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>APLOMB Technologies</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45738cf915b51235</t>
+          <t>https://www.indeed.com/viewjob?jk=3c7b8660e24dfc38</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Lake Forest, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, ELT, dbt, Tableau</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2b31f13d8496041</t>
+          <t>https://www.indeed.com/viewjob?jk=da3c07885d8b3693</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Fabric Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Marysville, OH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c7b8660e24dfc38</t>
+          <t>https://www.indeed.com/viewjob?jk=c9c434dda73e4155</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>UDR</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Lake Forest, IL, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da3c07885d8b3693</t>
+          <t>https://www.indeed.com/viewjob?jk=1fb77bd035c0b222</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Blackhawk Network</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Marysville, OH, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9c434dda73e4155</t>
+          <t>https://www.indeed.com/viewjob?jk=b3ee41a8c52420bf</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Senior Software Development Engineer (Site Reliability)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>UDR</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fb77bd035c0b222</t>
+          <t>https://www.indeed.com/viewjob?jk=56047e794a998d7c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr Snowflake/DWH/ETL Informatica Consultant</t>
+          <t>Senior Software Development Engineer (Site Reliability)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Hermitage Info Tech Llc</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Northbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb7813160ee888e4</t>
+          <t>https://www.indeed.com/viewjob?jk=728e137e29293bde</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Software Development Engineer (Site Reliability)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Blackhawk Network</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,42 +1571,42 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3ee41a8c52420bf</t>
+          <t>https://www.indeed.com/viewjob?jk=297ddc2108f979e1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer (Site Reliability)</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>RAZR Marketing, Inc.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, PostgreSQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56047e794a998d7c</t>
+          <t>https://www.indeed.com/viewjob?jk=7fde30b21f3e7647</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer (Site Reliability)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Intellisoft Technologies</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Northbrook, IL, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=728e137e29293bde</t>
+          <t>https://www.indeed.com/viewjob?jk=8c473d3620c861ac</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer (Site Reliability)</t>
+          <t>Platform Engineer SOW198 Datahub Platform</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=297ddc2108f979e1</t>
+          <t>https://www.indeed.com/viewjob?jk=0fab0a2c9cd2208f</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer 3 - Reston, VA - Freewheel</t>
+          <t>Senior Associate - Enterprise Intelligence Analytics Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Snowflake, ETL, dbt, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24d54b28b92ef5c9</t>
+          <t>https://www.indeed.com/viewjob?jk=f738fb7e1c97b094</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>Senior Associate - Senior Associate, Analytics Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>RAZR Marketing, Inc.</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, PostgreSQL, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Databricks, BigQuery, Scala, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, Git</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fde30b21f3e7647</t>
+          <t>https://www.indeed.com/viewjob?jk=6e6fe876bea05203</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Intellisoft Technologies</t>
+          <t>Vasa Fitness</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c473d3620c861ac</t>
+          <t>https://www.indeed.com/viewjob?jk=5ee3a253ea4b50de</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Platform Engineer SOW198 Datahub Platform</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fab0a2c9cd2208f</t>
+          <t>https://www.indeed.com/viewjob?jk=bc4bd1d0f1519ea1</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DevFinOps Engineer</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84a584e2ae5c7382</t>
+          <t>https://www.indeed.com/viewjob?jk=cf3f2dbb3812e475</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Associate - Enterprise Intelligence Analytics Engineer</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, dbt, Power BI</t>
+          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f738fb7e1c97b094</t>
+          <t>https://www.indeed.com/viewjob?jk=eeb8ab90439d98b8</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Associate - Senior Associate, Analytics Engineer</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Scala, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, Git</t>
+          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e6fe876bea05203</t>
+          <t>https://www.indeed.com/viewjob?jk=ea6ecf773d8deb21</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Molex</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Lisle, IL, US USA</t>
+          <t>Kearney, NE, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=461471cb36992ab7</t>
+          <t>https://www.indeed.com/viewjob?jk=a1d8f5634d6f6d76</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Associate</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Grand Island, NE, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, Spark, PySpark, Kafka, Snowflake, ETL, Splunk</t>
+          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54b42443ee3c4437</t>
+          <t>https://www.indeed.com/viewjob?jk=2ccaa9de6cb6d799</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc4bd1d0f1519ea1</t>
+          <t>https://www.indeed.com/viewjob?jk=47d6b37f8d80d085</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ALLO Communications</t>
+          <t>Molex</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Lisle, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf3f2dbb3812e475</t>
+          <t>https://www.indeed.com/viewjob?jk=461471cb36992ab7</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
+          <t>Associate</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ALLO Communications</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Hadoop, Hive, Spark, PySpark, Kafka, Snowflake, ETL, Splunk</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeb8ab90439d98b8</t>
+          <t>https://www.indeed.com/viewjob?jk=54b42443ee3c4437</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
+          <t>Data Engineer, Cat Digital Data &amp; AI</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ALLO Communications</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea6ecf773d8deb21</t>
+          <t>https://www.indeed.com/viewjob?jk=826181dbe0e126ae</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ALLO Communications</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Kearney, NE, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d8f5634d6f6d76</t>
+          <t>https://www.indeed.com/viewjob?jk=02fed8f682ea9929</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
+          <t>IT Data Solutions Developer - Intermediate</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ALLO Communications</t>
+          <t>Atrium Health</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Grand Island, NE, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ccaa9de6cb6d799</t>
+          <t>https://www.indeed.com/viewjob?jk=9c5097ade3e79b6c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
+          <t>Senior Software Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ALLO Communications</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47d6b37f8d80d085</t>
+          <t>https://www.indeed.com/viewjob?jk=4c67eab5c67331a9</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer, Cat Digital Data &amp; AI</t>
+          <t>Product Software Engineer I</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, Kinesis, Databricks, Spark, Scala, Kafka, Snowflake, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=826181dbe0e126ae</t>
+          <t>https://www.indeed.com/viewjob?jk=9c5d705afdfcef3f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>IT Data Solutions Developer - Intermediate</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Atrium Health</t>
+          <t>Blue Learning</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, ETL, ELT, dbt, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c5097ade3e79b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=1e8db13fab29835e</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Solutions Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>loanDepot</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02fed8f682ea9929</t>
+          <t>https://www.indeed.com/viewjob?jk=275de5114fc3f721</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - AI Innovation Team</t>
+          <t>Shopify Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes</t>
+          <t>AWS, S3, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=893eebcde0f6a410</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc5601c059bd73a</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Hybrid</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>GCON Inc</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c67eab5c67331a9</t>
+          <t>https://www.indeed.com/viewjob?jk=d9b57204f314618a</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Product Software Engineer I</t>
+          <t>Integration Developer - (8+ years w Java/Spring Boot Framework)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cloud and Things</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Databricks, Spark, Scala, Kafka, Snowflake, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Git</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2455,181 +2455,6 @@
         </is>
       </c>
       <c r="G58" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9c5d705afdfcef3f</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Blue Learning</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Lewisville, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, ETL, ELT, dbt, Tableau, Airflow</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1e8db13fab29835e</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Senior Cloud Solutions Engineer</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>loanDepot</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=275de5114fc3f721</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Shopify Architect</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Docker</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc5601c059bd73a</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>BI Developer</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>GCON Inc</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau, Airflow</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d9b57204f314618a</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Integration Developer - (8+ years w Java/Spring Boot Framework)</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Cloud and Things</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Brooklyn, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Git</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=6ef55b38d756ce85</t>
         </is>

--- a/results/job_matches_2026-06-20.xlsx
+++ b/results/job_matches_2026-06-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - AWS Glue / Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, Glue, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60c093da65d37212</t>
+          <t>https://www.indeed.com/viewjob?jk=4944b59a58404b8f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, API Gateway, RDS, Oracle, MySQL, DynamoDB, Splunk</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,94 +706,94 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2637106dd2c7c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=60c093da65d37212</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Consultant — System Integration &amp; MDM</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Triade Flevoland</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, ECS, RDS, Azure, Databricks, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Step Functions, API Gateway, RDS, Oracle, MySQL, DynamoDB, Splunk</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d22f323af4989133</t>
+          <t>https://www.indeed.com/viewjob?jk=f2637106dd2c7c5c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Feature Engineer</t>
+          <t>Consultant — System Integration &amp; MDM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Triade Flevoland</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, ECS, RDS, Azure, Databricks, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8442abf91777c1a</t>
+          <t>https://www.indeed.com/viewjob?jk=d22f323af4989133</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer/Database Administrator_ (Only W2)</t>
+          <t>Sr. Feature Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Chuwa America</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,59 +811,59 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adac783343467c24</t>
+          <t>https://www.indeed.com/viewjob?jk=b8442abf91777c1a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Snowflake Engineer</t>
+          <t>Data Engineer/Database Administrator_ (Only W2)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>Chuwa America</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, ETL, ELT, dbt</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf016976f76e7f0a</t>
+          <t>https://www.indeed.com/viewjob?jk=adac783343467c24</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Database Developer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Magnaflow</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Oceanside, CA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,77 +871,77 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, SQL Server, MySQL, NoSQL, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3505e51fdb71a895</t>
+          <t>https://www.indeed.com/viewjob?jk=6c2d8e205af354cd</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Information Products Team</t>
+          <t>Senior Snowflake Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Wellmark Blue Cross and Blue Shield</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Azure, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59625199b42cb5da</t>
+          <t>https://www.indeed.com/viewjob?jk=cf016976f76e7f0a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Database Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Magnaflow</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Oceanside, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, Data Modeling, ETL, ELT, Talend</t>
+          <t>Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, SQL Server, MySQL, NoSQL, Snowflake Schema</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6a583130162de58</t>
+          <t>https://www.indeed.com/viewjob?jk=3505e51fdb71a895</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Production Support Engineer</t>
+          <t>Senior Software Engineer - Information Products Team</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>IntelliLink Technologies</t>
+          <t>Wellmark Blue Cross and Blue Shield</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Azure, Spark, PySpark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=416511572a3a38ba</t>
+          <t>https://www.indeed.com/viewjob?jk=59625199b42cb5da</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Software Production Support Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Arc Technologies Group</t>
+          <t>IntelliLink Technologies</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af690b2327755c54</t>
+          <t>https://www.indeed.com/viewjob?jk=416511572a3a38ba</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer (SMTS / LMTS) - MDM</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Arc Technologies Group</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50844673569c1fb8</t>
+          <t>https://www.indeed.com/viewjob?jk=af690b2327755c54</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Full Stack Developer -In office, Alpharetta, GA</t>
+          <t>Data Engineer (SMTS / LMTS) - MDM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=789775eb6e130995</t>
+          <t>https://www.indeed.com/viewjob?jk=50844673569c1fb8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Digital Provider Software Development Engineer</t>
+          <t>Full Stack Developer -In office, Alpharetta, GA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8e58013e22bddb4</t>
+          <t>https://www.indeed.com/viewjob?jk=789775eb6e130995</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LSP</t>
+          <t>Digital Provider Software Development Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>project44</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d185ef3015154b1f</t>
+          <t>https://www.indeed.com/viewjob?jk=c8e58013e22bddb4</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Convey</t>
+          <t>project44</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46e5e7f505da6aea</t>
+          <t>https://www.indeed.com/viewjob?jk=d185ef3015154b1f</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Jr. Feature Engineer</t>
+          <t>Senior Software Engineer - LSP</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Convey</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3a9fd6adbb852f</t>
+          <t>https://www.indeed.com/viewjob?jk=46e5e7f505da6aea</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Jr. Feature Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Scala, Snowflake</t>
+          <t>Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372d6a67c10b163b</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3a9fd6adbb852f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>APLOMB Technologies</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45738cf915b51235</t>
+          <t>https://www.indeed.com/viewjob?jk=372d6a67c10b163b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Fabric Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>APLOMB Technologies</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c7b8660e24dfc38</t>
+          <t>https://www.indeed.com/viewjob?jk=45738cf915b51235</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Fabric Platform Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Lake Forest, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da3c07885d8b3693</t>
+          <t>https://www.indeed.com/viewjob?jk=3c7b8660e24dfc38</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Marysville, OH, US USA</t>
+          <t>Lake Forest, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9c434dda73e4155</t>
+          <t>https://www.indeed.com/viewjob?jk=da3c07885d8b3693</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>UDR</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>Marysville, OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fb77bd035c0b222</t>
+          <t>https://www.indeed.com/viewjob?jk=c9c434dda73e4155</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Blackhawk Network</t>
+          <t>UDR</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3ee41a8c52420bf</t>
+          <t>https://www.indeed.com/viewjob?jk=1fb77bd035c0b222</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer (Site Reliability)</t>
+          <t>Sr Fullstack Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56047e794a998d7c</t>
+          <t>https://www.indeed.com/viewjob?jk=e08b28ff2bdfcb80</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Northbrook, IL, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=728e137e29293bde</t>
+          <t>https://www.indeed.com/viewjob?jk=56047e794a998d7c</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Northbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=297ddc2108f979e1</t>
+          <t>https://www.indeed.com/viewjob?jk=728e137e29293bde</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>Senior Software Development Engineer (Site Reliability)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>RAZR Marketing, Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, PostgreSQL, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fde30b21f3e7647</t>
+          <t>https://www.indeed.com/viewjob?jk=297ddc2108f979e1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Intellisoft Technologies</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c473d3620c861ac</t>
+          <t>https://www.indeed.com/viewjob?jk=1d97244cd7329e73</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Platform Engineer SOW198 Datahub Platform</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>RAZR Marketing, Inc.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, PostgreSQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fab0a2c9cd2208f</t>
+          <t>https://www.indeed.com/viewjob?jk=7fde30b21f3e7647</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Associate - Enterprise Intelligence Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Intellisoft Technologies</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, dbt, Power BI</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f738fb7e1c97b094</t>
+          <t>https://www.indeed.com/viewjob?jk=8c473d3620c861ac</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Associate - Senior Associate, Analytics Engineer</t>
+          <t>Platform Engineer SOW198 Datahub Platform</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Scala, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e6fe876bea05203</t>
+          <t>https://www.indeed.com/viewjob?jk=0fab0a2c9cd2208f</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Associate - Enterprise Intelligence Analytics Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Vasa Fitness</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ee3a253ea4b50de</t>
+          <t>https://www.indeed.com/viewjob?jk=f738fb7e1c97b094</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
+          <t>Senior Associate - Senior Associate, Analytics Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ALLO Communications</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Databricks, BigQuery, Scala, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, Git</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc4bd1d0f1519ea1</t>
+          <t>https://www.indeed.com/viewjob?jk=6e6fe876bea05203</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ALLO Communications</t>
+          <t>Molex</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Lisle, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf3f2dbb3812e475</t>
+          <t>https://www.indeed.com/viewjob?jk=461471cb36992ab7</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
+          <t>Associate</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ALLO Communications</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Hadoop, Hive, Spark, PySpark, Kafka, Snowflake, ETL, Splunk</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeb8ab90439d98b8</t>
+          <t>https://www.indeed.com/viewjob?jk=54b42443ee3c4437</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ALLO Communications</t>
+          <t>Vasa Fitness</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea6ecf773d8deb21</t>
+          <t>https://www.indeed.com/viewjob?jk=5ee3a253ea4b50de</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Kearney, NE, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d8f5634d6f6d76</t>
+          <t>https://www.indeed.com/viewjob?jk=bc4bd1d0f1519ea1</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Grand Island, NE, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ccaa9de6cb6d799</t>
+          <t>https://www.indeed.com/viewjob?jk=cf3f2dbb3812e475</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47d6b37f8d80d085</t>
+          <t>https://www.indeed.com/viewjob?jk=eeb8ab90439d98b8</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Molex</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Lisle, IL, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=461471cb36992ab7</t>
+          <t>https://www.indeed.com/viewjob?jk=ea6ecf773d8deb21</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Associate</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Kearney, NE, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, Spark, PySpark, Kafka, Snowflake, ETL, Splunk</t>
+          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54b42443ee3c4437</t>
+          <t>https://www.indeed.com/viewjob?jk=a1d8f5634d6f6d76</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer, Cat Digital Data &amp; AI</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Grand Island, NE, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, GitHub Actions</t>
+          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=826181dbe0e126ae</t>
+          <t>https://www.indeed.com/viewjob?jk=2ccaa9de6cb6d799</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02fed8f682ea9929</t>
+          <t>https://www.indeed.com/viewjob?jk=47d6b37f8d80d085</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>IT Data Solutions Developer - Intermediate</t>
+          <t>Data Engineer, Cat Digital Data &amp; AI</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Atrium Health</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c5097ade3e79b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=826181dbe0e126ae</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Hybrid</t>
+          <t>IT Data Solutions Developer - Intermediate</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Atrium Health</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Azure DevOps, Terraform</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c67eab5c67331a9</t>
+          <t>https://www.indeed.com/viewjob?jk=9c5097ade3e79b6c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Product Software Engineer I</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Databricks, Spark, Scala, Kafka, Snowflake, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c5d705afdfcef3f</t>
+          <t>https://www.indeed.com/viewjob?jk=02fed8f682ea9929</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III - Python/PySpark/AWS</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Blue Learning</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, ETL, ELT, dbt, Tableau, Airflow</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e8db13fab29835e</t>
+          <t>https://www.indeed.com/viewjob?jk=7758e2775271790b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Cloud Solutions Engineer</t>
+          <t>Senior Software Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>loanDepot</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=275de5114fc3f721</t>
+          <t>https://www.indeed.com/viewjob?jk=4c67eab5c67331a9</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Shopify Architect</t>
+          <t>Product Software Engineer I</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Kinesis, Databricks, Spark, Scala, Kafka, Snowflake, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc5601c059bd73a</t>
+          <t>https://www.indeed.com/viewjob?jk=9c5d705afdfcef3f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>GCON Inc</t>
+          <t>Attain Finance</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau, Airflow</t>
+          <t>AWS, ECS, IAM, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9b57204f314618a</t>
+          <t>https://www.indeed.com/viewjob?jk=cb4fd37f5d5683cc</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Integration Developer - (8+ years w Java/Spring Boot Framework)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Cloud and Things</t>
+          <t>Blue Learning</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,15 +2446,190 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
+          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, ETL, ELT, dbt, Tableau, Airflow</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1e8db13fab29835e</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Senior Cloud Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>loanDepot</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=275de5114fc3f721</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>WFP Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Git</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=644f70485107abbe</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Shopify Architect</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Docker</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5bc5601c059bd73a</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>BI Developer</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>GCON Inc</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau, Airflow</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d9b57204f314618a</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Integration Developer - (8+ years w Java/Spring Boot Framework)</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Cloud and Things</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Brooklyn, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Git</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=6ef55b38d756ce85</t>
         </is>

--- a/results/job_matches_2026-06-20.xlsx
+++ b/results/job_matches_2026-06-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, Glue, Lambda, Step Functions, API Gateway, RDS, Oracle, MySQL, DynamoDB, Splunk</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60c093da65d37212</t>
+          <t>https://www.indeed.com/viewjob?jk=f2637106dd2c7c5c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Data Engineer- Full Time Opportunity, NOT C2C</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Codoxo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, API Gateway, RDS, Oracle, MySQL, DynamoDB, Splunk</t>
+          <t>AWS, Glue, S3, IAM, RDS, Spark, PySpark, Scala, PostgreSQL, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2637106dd2c7c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=780ec295f6bacdf5</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Digital Provider Software Development Engineer</t>
+          <t>Senior Software Engineer - LSP</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>project44</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8e58013e22bddb4</t>
+          <t>https://www.indeed.com/viewjob?jk=d185ef3015154b1f</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>project44</t>
+          <t>Convey</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d185ef3015154b1f</t>
+          <t>https://www.indeed.com/viewjob?jk=46e5e7f505da6aea</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LSP</t>
+          <t>Jr. Feature Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Convey</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46e5e7f505da6aea</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3a9fd6adbb852f</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Jr. Feature Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3a9fd6adbb852f</t>
+          <t>https://www.indeed.com/viewjob?jk=372d6a67c10b163b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>APLOMB Technologies</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372d6a67c10b163b</t>
+          <t>https://www.indeed.com/viewjob?jk=45738cf915b51235</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Fabric Platform Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>APLOMB Technologies</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45738cf915b51235</t>
+          <t>https://www.indeed.com/viewjob?jk=3c7b8660e24dfc38</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Fabric Platform Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lake Forest, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c7b8660e24dfc38</t>
+          <t>https://www.indeed.com/viewjob?jk=da3c07885d8b3693</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lake Forest, IL, US USA</t>
+          <t>Marysville, OH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da3c07885d8b3693</t>
+          <t>https://www.indeed.com/viewjob?jk=c9c434dda73e4155</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>UDR</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Marysville, OH, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9c434dda73e4155</t>
+          <t>https://www.indeed.com/viewjob?jk=1fb77bd035c0b222</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Sr Fullstack Developer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>UDR</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,67 +1476,67 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fb77bd035c0b222</t>
+          <t>https://www.indeed.com/viewjob?jk=e08b28ff2bdfcb80</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr Fullstack Developer</t>
+          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e08b28ff2bdfcb80</t>
+          <t>https://www.indeed.com/viewjob?jk=1d97244cd7329e73</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer (Site Reliability)</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>RAZR Marketing, Inc.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, PostgreSQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56047e794a998d7c</t>
+          <t>https://www.indeed.com/viewjob?jk=7fde30b21f3e7647</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer (Site Reliability)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Intellisoft Technologies</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Northbrook, IL, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=728e137e29293bde</t>
+          <t>https://www.indeed.com/viewjob?jk=8c473d3620c861ac</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer (Site Reliability)</t>
+          <t>Platform Engineer SOW198 Datahub Platform</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=297ddc2108f979e1</t>
+          <t>https://www.indeed.com/viewjob?jk=0fab0a2c9cd2208f</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Vasa Fitness</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d97244cd7329e73</t>
+          <t>https://www.indeed.com/viewjob?jk=5ee3a253ea4b50de</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RAZR Marketing, Inc.</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, PostgreSQL, Terraform, Docker, Kubernetes</t>
+          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fde30b21f3e7647</t>
+          <t>https://www.indeed.com/viewjob?jk=bc4bd1d0f1519ea1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Intellisoft Technologies</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c473d3620c861ac</t>
+          <t>https://www.indeed.com/viewjob?jk=cf3f2dbb3812e475</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Platform Engineer SOW198 Datahub Platform</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fab0a2c9cd2208f</t>
+          <t>https://www.indeed.com/viewjob?jk=eeb8ab90439d98b8</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Associate - Enterprise Intelligence Analytics Engineer</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, dbt, Power BI</t>
+          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f738fb7e1c97b094</t>
+          <t>https://www.indeed.com/viewjob?jk=ea6ecf773d8deb21</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Associate - Senior Associate, Analytics Engineer</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Kearney, NE, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Scala, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, Git</t>
+          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e6fe876bea05203</t>
+          <t>https://www.indeed.com/viewjob?jk=a1d8f5634d6f6d76</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Molex</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Lisle, IL, US USA</t>
+          <t>Grand Island, NE, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=461471cb36992ab7</t>
+          <t>https://www.indeed.com/viewjob?jk=2ccaa9de6cb6d799</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Associate</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, Spark, PySpark, Kafka, Snowflake, ETL, Splunk</t>
+          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54b42443ee3c4437</t>
+          <t>https://www.indeed.com/viewjob?jk=47d6b37f8d80d085</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Vasa Fitness</t>
+          <t>Molex</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Lisle, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, Glue, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ee3a253ea4b50de</t>
+          <t>https://www.indeed.com/viewjob?jk=461471cb36992ab7</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
+          <t>Associate</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ALLO Communications</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Hadoop, Hive, Spark, PySpark, Kafka, Snowflake, ETL, Splunk</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc4bd1d0f1519ea1</t>
+          <t>https://www.indeed.com/viewjob?jk=54b42443ee3c4437</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
+          <t>Data Engineer, Cat Digital Data &amp; AI</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ALLO Communications</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf3f2dbb3812e475</t>
+          <t>https://www.indeed.com/viewjob?jk=826181dbe0e126ae</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ALLO Communications</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeb8ab90439d98b8</t>
+          <t>https://www.indeed.com/viewjob?jk=02fed8f682ea9929</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
+          <t>IT Data Solutions Developer - Intermediate</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ALLO Communications</t>
+          <t>Atrium Health</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,67 +2071,67 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea6ecf773d8deb21</t>
+          <t>https://www.indeed.com/viewjob?jk=9c5097ade3e79b6c</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
+          <t>Software Engineer III - Python/PySpark/AWS</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ALLO Communications</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Kearney, NE, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d8f5634d6f6d76</t>
+          <t>https://www.indeed.com/viewjob?jk=7758e2775271790b</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
+          <t>Senior Software Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ALLO Communications</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Grand Island, NE, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ccaa9de6cb6d799</t>
+          <t>https://www.indeed.com/viewjob?jk=4c67eab5c67331a9</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ALLO Communications</t>
+          <t>Attain Finance</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, ECS, IAM, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47d6b37f8d80d085</t>
+          <t>https://www.indeed.com/viewjob?jk=cb4fd37f5d5683cc</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer, Cat Digital Data &amp; AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Blue Learning</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, GitHub Actions</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, ETL, ELT, dbt, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=826181dbe0e126ae</t>
+          <t>https://www.indeed.com/viewjob?jk=1e8db13fab29835e</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>IT Data Solutions Developer - Intermediate</t>
+          <t>Senior Cloud Solutions Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Atrium Health</t>
+          <t>loanDepot</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c5097ade3e79b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=275de5114fc3f721</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Shopify Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, S3, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,14 +2281,14 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02fed8f682ea9929</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc5601c059bd73a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer III - Python/PySpark/AWS</t>
+          <t>WFP Senior Data Scientist</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Git</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7758e2775271790b</t>
+          <t>https://www.indeed.com/viewjob?jk=644f70485107abbe</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Hybrid</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>GCON Inc</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c67eab5c67331a9</t>
+          <t>https://www.indeed.com/viewjob?jk=d9b57204f314618a</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Product Software Engineer I</t>
+          <t>Integration Developer - (8+ years w Java/Spring Boot Framework)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cloud and Things</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Databricks, Spark, Scala, Kafka, Snowflake, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2385,251 +2385,6 @@
         </is>
       </c>
       <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9c5d705afdfcef3f</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Senior Site Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Attain Finance</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Greenville, SC, US USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>AWS, ECS, IAM, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cb4fd37f5d5683cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Blue Learning</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Lewisville, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, ETL, ELT, dbt, Tableau, Airflow</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1e8db13fab29835e</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Senior Cloud Solutions Engineer</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>loanDepot</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=275de5114fc3f721</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>WFP Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Git</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=644f70485107abbe</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Shopify Architect</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Docker</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc5601c059bd73a</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>BI Developer</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>GCON Inc</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau, Airflow</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d9b57204f314618a</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Integration Developer - (8+ years w Java/Spring Boot Framework)</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Cloud and Things</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Brooklyn, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Git</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=6ef55b38d756ce85</t>
         </is>

--- a/results/job_matches_2026-06-20.xlsx
+++ b/results/job_matches_2026-06-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,52 +818,52 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer/Database Administrator_ (Only W2)</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Chuwa America</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adac783343467c24</t>
+          <t>https://www.indeed.com/viewjob?jk=6c2d8e205af354cd</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Snowflake Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c2d8e205af354cd</t>
+          <t>https://www.indeed.com/viewjob?jk=cf016976f76e7f0a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Snowflake Engineer</t>
+          <t>Database Developer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>Magnaflow</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Oceanside, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,42 +906,42 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, ETL, ELT, dbt</t>
+          <t>Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, SQL Server, MySQL, NoSQL, Snowflake Schema</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf016976f76e7f0a</t>
+          <t>https://www.indeed.com/viewjob?jk=3505e51fdb71a895</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Database Developer</t>
+          <t>Software Production Support Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Magnaflow</t>
+          <t>IntelliLink Technologies</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Oceanside, CA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, SQL Server, MySQL, NoSQL, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3505e51fdb71a895</t>
+          <t>https://www.indeed.com/viewjob?jk=416511572a3a38ba</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Information Products Team</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Wellmark Blue Cross and Blue Shield</t>
+          <t>Arc Technologies Group</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Azure, Spark, PySpark</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59625199b42cb5da</t>
+          <t>https://www.indeed.com/viewjob?jk=af690b2327755c54</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Production Support Engineer</t>
+          <t>Data Engineer (SMTS / LMTS) - MDM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IntelliLink Technologies</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=416511572a3a38ba</t>
+          <t>https://www.indeed.com/viewjob?jk=50844673569c1fb8</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Full Stack Developer -In office, Alpharetta, GA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Arc Technologies Group</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,19 +1056,19 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af690b2327755c54</t>
+          <t>https://www.indeed.com/viewjob?jk=789775eb6e130995</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer (SMTS / LMTS) - MDM</t>
+          <t>Senior Software Engineer - LSP</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>project44</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, ELT, Airflow</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50844673569c1fb8</t>
+          <t>https://www.indeed.com/viewjob?jk=d185ef3015154b1f</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Full Stack Developer -In office, Alpharetta, GA</t>
+          <t>Jr. Feature Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=789775eb6e130995</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3a9fd6adbb852f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LSP</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>project44</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d185ef3015154b1f</t>
+          <t>https://www.indeed.com/viewjob?jk=372d6a67c10b163b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LSP</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Convey</t>
+          <t>APLOMB Technologies</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46e5e7f505da6aea</t>
+          <t>https://www.indeed.com/viewjob?jk=45738cf915b51235</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Jr. Feature Engineer</t>
+          <t>Fabric Platform Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3a9fd6adbb852f</t>
+          <t>https://www.indeed.com/viewjob?jk=7b1831e001122e4d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Fabric Platform Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372d6a67c10b163b</t>
+          <t>https://www.indeed.com/viewjob?jk=3c7b8660e24dfc38</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>APLOMB Technologies</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Lake Forest, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45738cf915b51235</t>
+          <t>https://www.indeed.com/viewjob?jk=da3c07885d8b3693</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Fabric Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Marysville, OH, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c7b8660e24dfc38</t>
+          <t>https://www.indeed.com/viewjob?jk=c9c434dda73e4155</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>UDR</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Lake Forest, IL, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da3c07885d8b3693</t>
+          <t>https://www.indeed.com/viewjob?jk=1fb77bd035c0b222</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Fullstack Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Marysville, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,67 +1406,67 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9c434dda73e4155</t>
+          <t>https://www.indeed.com/viewjob?jk=e08b28ff2bdfcb80</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>UDR</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fb77bd035c0b222</t>
+          <t>https://www.indeed.com/viewjob?jk=1d97244cd7329e73</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr Fullstack Developer</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>RAZR Marketing, Inc.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, PostgreSQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e08b28ff2bdfcb80</t>
+          <t>https://www.indeed.com/viewjob?jk=7fde30b21f3e7647</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Intellisoft Technologies</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d97244cd7329e73</t>
+          <t>https://www.indeed.com/viewjob?jk=8c473d3620c861ac</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>Platform Engineer SOW198 Datahub Platform</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>RAZR Marketing, Inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, PostgreSQL, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fde30b21f3e7647</t>
+          <t>https://www.indeed.com/viewjob?jk=0fab0a2c9cd2208f</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Intellisoft Technologies</t>
+          <t>Vasa Fitness</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c473d3620c861ac</t>
+          <t>https://www.indeed.com/viewjob?jk=5ee3a253ea4b50de</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Platform Engineer SOW198 Datahub Platform</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fab0a2c9cd2208f</t>
+          <t>https://www.indeed.com/viewjob?jk=bc4bd1d0f1519ea1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Vasa Fitness</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
+          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ee3a253ea4b50de</t>
+          <t>https://www.indeed.com/viewjob?jk=cf3f2dbb3812e475</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc4bd1d0f1519ea1</t>
+          <t>https://www.indeed.com/viewjob?jk=eeb8ab90439d98b8</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf3f2dbb3812e475</t>
+          <t>https://www.indeed.com/viewjob?jk=ea6ecf773d8deb21</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Kearney, NE, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeb8ab90439d98b8</t>
+          <t>https://www.indeed.com/viewjob?jk=a1d8f5634d6f6d76</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Grand Island, NE, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea6ecf773d8deb21</t>
+          <t>https://www.indeed.com/viewjob?jk=2ccaa9de6cb6d799</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Kearney, NE, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d8f5634d6f6d76</t>
+          <t>https://www.indeed.com/viewjob?jk=47d6b37f8d80d085</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ALLO Communications</t>
+          <t>Molex</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Grand Island, NE, US USA</t>
+          <t>Lisle, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ccaa9de6cb6d799</t>
+          <t>https://www.indeed.com/viewjob?jk=461471cb36992ab7</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
+          <t>Associate</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ALLO Communications</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Hadoop, Hive, Spark, PySpark, Kafka, Snowflake, ETL, Splunk</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47d6b37f8d80d085</t>
+          <t>https://www.indeed.com/viewjob?jk=54b42443ee3c4437</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>Data Engineer, Cat Digital Data &amp; AI</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Molex</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Lisle, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=461471cb36992ab7</t>
+          <t>https://www.indeed.com/viewjob?jk=826181dbe0e126ae</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Associate</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, Spark, PySpark, Kafka, Snowflake, ETL, Splunk</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54b42443ee3c4437</t>
+          <t>https://www.indeed.com/viewjob?jk=02fed8f682ea9929</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer, Cat Digital Data &amp; AI</t>
+          <t>IT Data Solutions Developer - Intermediate</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Atrium Health</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, GitHub Actions</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,67 +2001,67 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=826181dbe0e126ae</t>
+          <t>https://www.indeed.com/viewjob?jk=9c5097ade3e79b6c</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III - Python/PySpark/AWS</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02fed8f682ea9929</t>
+          <t>https://www.indeed.com/viewjob?jk=7758e2775271790b</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>IT Data Solutions Developer - Intermediate</t>
+          <t>Senior Software Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Atrium Health</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c5097ade3e79b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=4c67eab5c67331a9</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer III - Python/PySpark/AWS</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Attain Finance</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, ECS, IAM, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7758e2775271790b</t>
+          <t>https://www.indeed.com/viewjob?jk=cb4fd37f5d5683cc</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Hybrid</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Blue Learning</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Azure DevOps, Terraform</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, ETL, ELT, dbt, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c67eab5c67331a9</t>
+          <t>https://www.indeed.com/viewjob?jk=1e8db13fab29835e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Cloud Solutions Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Attain Finance</t>
+          <t>loanDepot</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb4fd37f5d5683cc</t>
+          <t>https://www.indeed.com/viewjob?jk=275de5114fc3f721</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Shopify Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Blue Learning</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, ETL, ELT, dbt, Tableau, Airflow</t>
+          <t>AWS, S3, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e8db13fab29835e</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc5601c059bd73a</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Cloud Solutions Engineer</t>
+          <t>WFP Senior Data Scientist</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>loanDepot</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=275de5114fc3f721</t>
+          <t>https://www.indeed.com/viewjob?jk=644f70485107abbe</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Shopify Architect</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>GCON Inc</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc5601c059bd73a</t>
+          <t>https://www.indeed.com/viewjob?jk=d9b57204f314618a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>WFP Senior Data Scientist</t>
+          <t>Integration Developer - (8+ years w Java/Spring Boot Framework)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Cloud and Things</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,85 +2306,15 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Git</t>
+          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Git</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=644f70485107abbe</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>BI Developer</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>GCON Inc</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau, Airflow</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d9b57204f314618a</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Integration Developer - (8+ years w Java/Spring Boot Framework)</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Cloud and Things</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Brooklyn, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Git</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=6ef55b38d756ce85</t>
         </is>

--- a/results/job_matches_2026-06-20.xlsx
+++ b/results/job_matches_2026-06-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,87 +783,87 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Feature Engineer</t>
+          <t>Full Stack Developer React/ Java/ Python</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Middletown, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8442abf91777c1a</t>
+          <t>https://www.indeed.com/viewjob?jk=d29d621da3e9a4ef</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Sr. Feature Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c2d8e205af354cd</t>
+          <t>https://www.indeed.com/viewjob?jk=b8442abf91777c1a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Snowflake Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf016976f76e7f0a</t>
+          <t>https://www.indeed.com/viewjob?jk=6c2d8e205af354cd</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Database Developer</t>
+          <t>Senior Snowflake Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Magnaflow</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Oceanside, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,42 +906,42 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, SQL Server, MySQL, NoSQL, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3505e51fdb71a895</t>
+          <t>https://www.indeed.com/viewjob?jk=cf016976f76e7f0a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Production Support Engineer</t>
+          <t>Database Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>IntelliLink Technologies</t>
+          <t>Magnaflow</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Oceanside, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins</t>
+          <t>Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, SQL Server, MySQL, NoSQL, Snowflake Schema</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=416511572a3a38ba</t>
+          <t>https://www.indeed.com/viewjob?jk=3505e51fdb71a895</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Software Production Support Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Arc Technologies Group</t>
+          <t>IntelliLink Technologies</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af690b2327755c54</t>
+          <t>https://www.indeed.com/viewjob?jk=416511572a3a38ba</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer (SMTS / LMTS) - MDM</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Arc Technologies Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50844673569c1fb8</t>
+          <t>https://www.indeed.com/viewjob?jk=af690b2327755c54</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Full Stack Developer -In office, Alpharetta, GA</t>
+          <t>Data Engineer (SMTS / LMTS) - MDM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=789775eb6e130995</t>
+          <t>https://www.indeed.com/viewjob?jk=50844673569c1fb8</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LSP</t>
+          <t>Full Stack Developer -In office, Alpharetta, GA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>project44</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d185ef3015154b1f</t>
+          <t>https://www.indeed.com/viewjob?jk=789775eb6e130995</t>
         </is>
       </c>
     </row>
@@ -1168,17 +1168,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Fabric Platform Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>APLOMB Technologies</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45738cf915b51235</t>
+          <t>https://www.indeed.com/viewjob?jk=7b1831e001122e4d</t>
         </is>
       </c>
     </row>
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b1831e001122e4d</t>
+          <t>https://www.indeed.com/viewjob?jk=3c7b8660e24dfc38</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Fabric Platform Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lake Forest, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c7b8660e24dfc38</t>
+          <t>https://www.indeed.com/viewjob?jk=da3c07885d8b3693</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lake Forest, IL, US USA</t>
+          <t>Marysville, OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da3c07885d8b3693</t>
+          <t>https://www.indeed.com/viewjob?jk=c9c434dda73e4155</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>UDR</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Marysville, OH, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9c434dda73e4155</t>
+          <t>https://www.indeed.com/viewjob?jk=1fb77bd035c0b222</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Sr Fullstack Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>UDR</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,59 +1371,59 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fb77bd035c0b222</t>
+          <t>https://www.indeed.com/viewjob?jk=e08b28ff2bdfcb80</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr Fullstack Developer</t>
+          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e08b28ff2bdfcb80</t>
+          <t>https://www.indeed.com/viewjob?jk=1d97244cd7329e73</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>RAZR Marketing, Inc.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, PostgreSQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d97244cd7329e73</t>
+          <t>https://www.indeed.com/viewjob?jk=7fde30b21f3e7647</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>RAZR Marketing, Inc.</t>
+          <t>Intellisoft Technologies</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, PostgreSQL, Terraform, Docker, Kubernetes</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fde30b21f3e7647</t>
+          <t>https://www.indeed.com/viewjob?jk=8c473d3620c861ac</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Platform Engineer SOW198 Datahub Platform</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Intellisoft Technologies</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c473d3620c861ac</t>
+          <t>https://www.indeed.com/viewjob?jk=0fab0a2c9cd2208f</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Platform Engineer SOW198 Datahub Platform</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Molex</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Lisle, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Glue, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fab0a2c9cd2208f</t>
+          <t>https://www.indeed.com/viewjob?jk=461471cb36992ab7</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Associate</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Vasa Fitness</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
+          <t>RDS, Azure, Hadoop, Hive, Spark, PySpark, Kafka, Snowflake, ETL, Splunk</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ee3a253ea4b50de</t>
+          <t>https://www.indeed.com/viewjob?jk=54b42443ee3c4437</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ALLO Communications</t>
+          <t>Vasa Fitness</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc4bd1d0f1519ea1</t>
+          <t>https://www.indeed.com/viewjob?jk=5ee3a253ea4b50de</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf3f2dbb3812e475</t>
+          <t>https://www.indeed.com/viewjob?jk=bc4bd1d0f1519ea1</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeb8ab90439d98b8</t>
+          <t>https://www.indeed.com/viewjob?jk=cf3f2dbb3812e475</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea6ecf773d8deb21</t>
+          <t>https://www.indeed.com/viewjob?jk=eeb8ab90439d98b8</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kearney, NE, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d8f5634d6f6d76</t>
+          <t>https://www.indeed.com/viewjob?jk=ea6ecf773d8deb21</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Grand Island, NE, US USA</t>
+          <t>Kearney, NE, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ccaa9de6cb6d799</t>
+          <t>https://www.indeed.com/viewjob?jk=a1d8f5634d6f6d76</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Grand Island, NE, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47d6b37f8d80d085</t>
+          <t>https://www.indeed.com/viewjob?jk=2ccaa9de6cb6d799</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Molex</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Lisle, IL, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=461471cb36992ab7</t>
+          <t>https://www.indeed.com/viewjob?jk=47d6b37f8d80d085</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Associate</t>
+          <t>Data Engineer, Cat Digital Data &amp; AI</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, Spark, PySpark, Kafka, Snowflake, ETL, Splunk</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54b42443ee3c4437</t>
+          <t>https://www.indeed.com/viewjob?jk=826181dbe0e126ae</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer, Cat Digital Data &amp; AI</t>
+          <t>IT Data Solutions Developer - Intermediate</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Atrium Health</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, GitHub Actions</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,67 +1931,67 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=826181dbe0e126ae</t>
+          <t>https://www.indeed.com/viewjob?jk=9c5097ade3e79b6c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III - Python/PySpark/AWS</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02fed8f682ea9929</t>
+          <t>https://www.indeed.com/viewjob?jk=7758e2775271790b</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>IT Data Solutions Developer - Intermediate</t>
+          <t>Senior Software Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Atrium Health</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c5097ade3e79b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=4c67eab5c67331a9</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer III - Python/PySpark/AWS</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Attain Finance</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, ECS, IAM, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7758e2775271790b</t>
+          <t>https://www.indeed.com/viewjob?jk=cb4fd37f5d5683cc</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Hybrid</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Blue Learning</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Azure DevOps, Terraform</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, ETL, ELT, dbt, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c67eab5c67331a9</t>
+          <t>https://www.indeed.com/viewjob?jk=1e8db13fab29835e</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Cloud Solutions Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Attain Finance</t>
+          <t>loanDepot</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb4fd37f5d5683cc</t>
+          <t>https://www.indeed.com/viewjob?jk=275de5114fc3f721</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Shopify Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Blue Learning</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, ETL, ELT, dbt, Tableau, Airflow</t>
+          <t>AWS, S3, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e8db13fab29835e</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc5601c059bd73a</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Cloud Solutions Engineer</t>
+          <t>WFP Senior Data Scientist</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>loanDepot</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Git</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=275de5114fc3f721</t>
+          <t>https://www.indeed.com/viewjob?jk=644f70485107abbe</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Shopify Architect</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>GCON Inc</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,112 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc5601c059bd73a</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>WFP Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Git</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=644f70485107abbe</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>BI Developer</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>GCON Inc</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau, Airflow</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=d9b57204f314618a</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Integration Developer - (8+ years w Java/Spring Boot Framework)</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Cloud and Things</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Brooklyn, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Git</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6ef55b38d756ce85</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-20.xlsx
+++ b/results/job_matches_2026-06-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Consultant — System Integration &amp; MDM</t>
+          <t>Full Stack Developer React/ Java/ Python</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Triade Flevoland</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Middletown, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,104 +766,104 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, ECS, RDS, Azure, Databricks, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d22f323af4989133</t>
+          <t>https://www.indeed.com/viewjob?jk=d29d621da3e9a4ef</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Full Stack Developer React/ Java/ Python</t>
+          <t>Sr. Feature Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Middletown, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d29d621da3e9a4ef</t>
+          <t>https://www.indeed.com/viewjob?jk=b8442abf91777c1a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Feature Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8442abf91777c1a</t>
+          <t>https://www.indeed.com/viewjob?jk=6c2d8e205af354cd</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Snowflake Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c2d8e205af354cd</t>
+          <t>https://www.indeed.com/viewjob?jk=cf016976f76e7f0a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Snowflake Engineer</t>
+          <t>Database Developer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>Magnaflow</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Oceanside, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,42 +906,42 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, ETL, ELT, dbt</t>
+          <t>Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, SQL Server, MySQL, NoSQL, Snowflake Schema</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf016976f76e7f0a</t>
+          <t>https://www.indeed.com/viewjob?jk=3505e51fdb71a895</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Database Developer</t>
+          <t>Software Production Support Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Magnaflow</t>
+          <t>IntelliLink Technologies</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Oceanside, CA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, SQL Server, MySQL, NoSQL, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3505e51fdb71a895</t>
+          <t>https://www.indeed.com/viewjob?jk=416511572a3a38ba</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Production Support Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>IntelliLink Technologies</t>
+          <t>Arc Technologies Group</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=416511572a3a38ba</t>
+          <t>https://www.indeed.com/viewjob?jk=af690b2327755c54</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Data Engineer (SMTS / LMTS) - MDM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Arc Technologies Group</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af690b2327755c54</t>
+          <t>https://www.indeed.com/viewjob?jk=50844673569c1fb8</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer (SMTS / LMTS) - MDM</t>
+          <t>Full Stack Developer -In office, Alpharetta, GA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, ELT, Airflow</t>
+          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50844673569c1fb8</t>
+          <t>https://www.indeed.com/viewjob?jk=789775eb6e130995</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Full Stack Developer -In office, Alpharetta, GA</t>
+          <t>Jr. Feature Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,14 +1091,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=789775eb6e130995</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3a9fd6adbb852f</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Jr. Feature Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3a9fd6adbb852f</t>
+          <t>https://www.indeed.com/viewjob?jk=372d6a67c10b163b</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Fabric Platform Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372d6a67c10b163b</t>
+          <t>https://www.indeed.com/viewjob?jk=7b1831e001122e4d</t>
         </is>
       </c>
     </row>
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b1831e001122e4d</t>
+          <t>https://www.indeed.com/viewjob?jk=3c7b8660e24dfc38</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Fabric Platform Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lake Forest, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c7b8660e24dfc38</t>
+          <t>https://www.indeed.com/viewjob?jk=da3c07885d8b3693</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lake Forest, IL, US USA</t>
+          <t>Marysville, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da3c07885d8b3693</t>
+          <t>https://www.indeed.com/viewjob?jk=c9c434dda73e4155</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Fullstack Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Marysville, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,67 +1301,67 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9c434dda73e4155</t>
+          <t>https://www.indeed.com/viewjob?jk=e08b28ff2bdfcb80</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>UDR</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fb77bd035c0b222</t>
+          <t>https://www.indeed.com/viewjob?jk=1d97244cd7329e73</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr Fullstack Developer</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>RAZR Marketing, Inc.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, PostgreSQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e08b28ff2bdfcb80</t>
+          <t>https://www.indeed.com/viewjob?jk=7fde30b21f3e7647</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Intellisoft Technologies</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d97244cd7329e73</t>
+          <t>https://www.indeed.com/viewjob?jk=8c473d3620c861ac</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>RAZR Marketing, Inc.</t>
+          <t>Molex</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Lisle, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, PostgreSQL, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fde30b21f3e7647</t>
+          <t>https://www.indeed.com/viewjob?jk=461471cb36992ab7</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Intellisoft Technologies</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>RDS, Azure, Hadoop, Hive, Spark, PySpark, Kafka, Snowflake, ETL, Splunk</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c473d3620c861ac</t>
+          <t>https://www.indeed.com/viewjob?jk=54b42443ee3c4437</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Platform Engineer SOW198 Datahub Platform</t>
+          <t>Data Engineer, Cat Digital Data &amp; AI</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fab0a2c9cd2208f</t>
+          <t>https://www.indeed.com/viewjob?jk=826181dbe0e126ae</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Molex</t>
+          <t>Vasa Fitness</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lisle, IL, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=461471cb36992ab7</t>
+          <t>https://www.indeed.com/viewjob?jk=5ee3a253ea4b50de</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Associate</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, Spark, PySpark, Kafka, Snowflake, ETL, Splunk</t>
+          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54b42443ee3c4437</t>
+          <t>https://www.indeed.com/viewjob?jk=bc4bd1d0f1519ea1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Vasa Fitness</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
+          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ee3a253ea4b50de</t>
+          <t>https://www.indeed.com/viewjob?jk=cf3f2dbb3812e475</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc4bd1d0f1519ea1</t>
+          <t>https://www.indeed.com/viewjob?jk=eeb8ab90439d98b8</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf3f2dbb3812e475</t>
+          <t>https://www.indeed.com/viewjob?jk=ea6ecf773d8deb21</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Kearney, NE, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeb8ab90439d98b8</t>
+          <t>https://www.indeed.com/viewjob?jk=a1d8f5634d6f6d76</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Grand Island, NE, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea6ecf773d8deb21</t>
+          <t>https://www.indeed.com/viewjob?jk=2ccaa9de6cb6d799</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Kearney, NE, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d8f5634d6f6d76</t>
+          <t>https://www.indeed.com/viewjob?jk=47d6b37f8d80d085</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
+          <t>IT Data Solutions Developer - Intermediate</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ALLO Communications</t>
+          <t>Atrium Health</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Grand Island, NE, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,67 +1826,67 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ccaa9de6cb6d799</t>
+          <t>https://www.indeed.com/viewjob?jk=9c5097ade3e79b6c</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
+          <t>Software Engineer III - Python/PySpark/AWS</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ALLO Communications</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47d6b37f8d80d085</t>
+          <t>https://www.indeed.com/viewjob?jk=7758e2775271790b</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer, Cat Digital Data &amp; AI</t>
+          <t>Senior Software Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=826181dbe0e126ae</t>
+          <t>https://www.indeed.com/viewjob?jk=4c67eab5c67331a9</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>IT Data Solutions Developer - Intermediate</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Atrium Health</t>
+          <t>Attain Finance</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, ECS, IAM, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c5097ade3e79b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=cb4fd37f5d5683cc</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer III - Python/PySpark/AWS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Blue Learning</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, ETL, ELT, dbt, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7758e2775271790b</t>
+          <t>https://www.indeed.com/viewjob?jk=1e8db13fab29835e</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Hybrid</t>
+          <t>Shopify Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, S3, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c67eab5c67331a9</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc5601c059bd73a</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>WFP Senior Data Scientist</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Attain Finance</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Git</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb4fd37f5d5683cc</t>
+          <t>https://www.indeed.com/viewjob?jk=644f70485107abbe</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Blue Learning</t>
+          <t>GCON Inc</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, ETL, ELT, dbt, Tableau, Airflow</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2070,146 +2070,6 @@
         </is>
       </c>
       <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1e8db13fab29835e</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Senior Cloud Solutions Engineer</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>loanDepot</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=275de5114fc3f721</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Shopify Architect</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Docker</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc5601c059bd73a</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>WFP Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Git</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=644f70485107abbe</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>BI Developer</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>GCON Inc</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau, Airflow</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d9b57204f314618a</t>
         </is>

--- a/results/job_matches_2026-06-20.xlsx
+++ b/results/job_matches_2026-06-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DevOps Engineer - IN PERSON - WIXOM MI</t>
+          <t>Data Engineer C1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>J&amp;B Medical</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Wixom, MI, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, RDS, Azure, GCP, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2db67e76b3a6ec5</t>
+          <t>https://www.indeed.com/viewjob?jk=bd7a10fab4aead6b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer C1</t>
+          <t>Sr. Associate, Site Reliability Engineering</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala, Kafka</t>
+          <t>AWS, Lambda, Athena, S3, API Gateway, ECS, IAM, RDS, Azure, Databricks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,49 +566,49 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd7a10fab4aead6b</t>
+          <t>https://www.indeed.com/viewjob?jk=1d58654d97d98c4a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior IT Big Data Developer</t>
+          <t>Software Engineer III - AWS Glue / Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a6a3f2e51311a48</t>
+          <t>https://www.indeed.com/viewjob?jk=4944b59a58404b8f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Associate, Site Reliability Engineering</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -622,11 +622,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, API Gateway, ECS, IAM, RDS, Azure, Databricks</t>
+          <t>AWS, Glue, Lambda, Step Functions, API Gateway, RDS, Oracle, MySQL, DynamoDB, Splunk</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,102 +636,102 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d58654d97d98c4a</t>
+          <t>https://www.indeed.com/viewjob?jk=f2637106dd2c7c5c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS Glue / Data Engineer</t>
+          <t>Data Engineer- Full Time Opportunity, NOT C2C</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Codoxo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, S3, IAM, RDS, Spark, PySpark, Scala, PostgreSQL, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4944b59a58404b8f</t>
+          <t>https://www.indeed.com/viewjob?jk=780ec295f6bacdf5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Full Stack Developer React/ Java/ Python</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Middletown, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, API Gateway, RDS, Oracle, MySQL, DynamoDB, Splunk</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2637106dd2c7c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=d29d621da3e9a4ef</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer- Full Time Opportunity, NOT C2C</t>
+          <t>Sr. Feature Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Codoxo</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Spark, PySpark, Scala, PostgreSQL, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=780ec295f6bacdf5</t>
+          <t>https://www.indeed.com/viewjob?jk=b8442abf91777c1a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Full Stack Developer React/ Java/ Python</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Middletown, NJ, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,19 +776,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d29d621da3e9a4ef</t>
+          <t>https://www.indeed.com/viewjob?jk=6c2d8e205af354cd</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Feature Engineer</t>
+          <t>Senior Snowflake Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -797,38 +797,38 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8442abf91777c1a</t>
+          <t>https://www.indeed.com/viewjob?jk=cf016976f76e7f0a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Fresh Food QA Technician</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>7-Eleven</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c2d8e205af354cd</t>
+          <t>https://www.indeed.com/viewjob?jk=4195bab3d9303fad</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Snowflake Engineer</t>
+          <t>Software Production Support Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>IntelliLink Technologies</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf016976f76e7f0a</t>
+          <t>https://www.indeed.com/viewjob?jk=416511572a3a38ba</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Database Developer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Magnaflow</t>
+          <t>Arc Technologies Group</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Oceanside, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, SQL Server, MySQL, NoSQL, Snowflake Schema</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3505e51fdb71a895</t>
+          <t>https://www.indeed.com/viewjob?jk=af690b2327755c54</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Production Support Engineer</t>
+          <t>Jr. Feature Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>IntelliLink Technologies</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins</t>
+          <t>Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=416511572a3a38ba</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3a9fd6adbb852f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Arc Technologies Group</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af690b2327755c54</t>
+          <t>https://www.indeed.com/viewjob?jk=372d6a67c10b163b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer (SMTS / LMTS) - MDM</t>
+          <t>Fabric Platform Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50844673569c1fb8</t>
+          <t>https://www.indeed.com/viewjob?jk=7b1831e001122e4d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Full Stack Developer -In office, Alpharetta, GA</t>
+          <t>Fabric Platform Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=789775eb6e130995</t>
+          <t>https://www.indeed.com/viewjob?jk=3c7b8660e24dfc38</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Jr. Feature Engineer</t>
+          <t>Sr Fullstack Developer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,67 +1091,67 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3a9fd6adbb852f</t>
+          <t>https://www.indeed.com/viewjob?jk=e08b28ff2bdfcb80</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372d6a67c10b163b</t>
+          <t>https://www.indeed.com/viewjob?jk=1d97244cd7329e73</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Fabric Platform Engineer</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>RAZR Marketing, Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, PostgreSQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,67 +1161,67 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b1831e001122e4d</t>
+          <t>https://www.indeed.com/viewjob?jk=7fde30b21f3e7647</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Fabric Platform Engineer</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Molex</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lisle, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c7b8660e24dfc38</t>
+          <t>https://www.indeed.com/viewjob?jk=461471cb36992ab7</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Associate</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lake Forest, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Hadoop, Hive, Spark, PySpark, Kafka, Snowflake, ETL, Splunk</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da3c07885d8b3693</t>
+          <t>https://www.indeed.com/viewjob?jk=54b42443ee3c4437</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer, Cat Digital Data &amp; AI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Marysville, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9c434dda73e4155</t>
+          <t>https://www.indeed.com/viewjob?jk=826181dbe0e126ae</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr Fullstack Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Vasa Fitness</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e08b28ff2bdfcb80</t>
+          <t>https://www.indeed.com/viewjob?jk=5ee3a253ea4b50de</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
+          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d97244cd7329e73</t>
+          <t>https://www.indeed.com/viewjob?jk=bc4bd1d0f1519ea1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>RAZR Marketing, Inc.</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, PostgreSQL, Terraform, Docker, Kubernetes</t>
+          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fde30b21f3e7647</t>
+          <t>https://www.indeed.com/viewjob?jk=cf3f2dbb3812e475</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Intellisoft Technologies</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c473d3620c861ac</t>
+          <t>https://www.indeed.com/viewjob?jk=eeb8ab90439d98b8</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Molex</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Lisle, IL, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=461471cb36992ab7</t>
+          <t>https://www.indeed.com/viewjob?jk=ea6ecf773d8deb21</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Associate</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Kearney, NE, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, Spark, PySpark, Kafka, Snowflake, ETL, Splunk</t>
+          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54b42443ee3c4437</t>
+          <t>https://www.indeed.com/viewjob?jk=a1d8f5634d6f6d76</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer, Cat Digital Data &amp; AI</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Grand Island, NE, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, GitHub Actions</t>
+          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=826181dbe0e126ae</t>
+          <t>https://www.indeed.com/viewjob?jk=2ccaa9de6cb6d799</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Vasa Fitness</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
+          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ee3a253ea4b50de</t>
+          <t>https://www.indeed.com/viewjob?jk=47d6b37f8d80d085</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
+          <t>IT Data Solutions Developer - Intermediate</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ALLO Communications</t>
+          <t>Atrium Health</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,67 +1581,67 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc4bd1d0f1519ea1</t>
+          <t>https://www.indeed.com/viewjob?jk=9c5097ade3e79b6c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
+          <t>Software Engineer III - Python/PySpark/AWS</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ALLO Communications</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf3f2dbb3812e475</t>
+          <t>https://www.indeed.com/viewjob?jk=7758e2775271790b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
+          <t>Senior Software Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ALLO Communications</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeb8ab90439d98b8</t>
+          <t>https://www.indeed.com/viewjob?jk=4c67eab5c67331a9</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ALLO Communications</t>
+          <t>Attain Finance</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, ECS, IAM, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea6ecf773d8deb21</t>
+          <t>https://www.indeed.com/viewjob?jk=cb4fd37f5d5683cc</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ALLO Communications</t>
+          <t>Blue Learning</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kearney, NE, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, ETL, ELT, dbt, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d8f5634d6f6d76</t>
+          <t>https://www.indeed.com/viewjob?jk=1e8db13fab29835e</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
+          <t>Shopify Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ALLO Communications</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Grand Island, NE, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,322 +1756,42 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ccaa9de6cb6d799</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc5601c059bd73a</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
+          <t>WFP Senior Data Scientist</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ALLO Communications</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Git</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47d6b37f8d80d085</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>IT Data Solutions Developer - Intermediate</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Atrium Health</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9c5097ade3e79b6c</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Software Engineer III - Python/PySpark/AWS</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7758e2775271790b</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Hybrid</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Mayo Clinic</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Rochester, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4c67eab5c67331a9</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Senior Site Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Attain Finance</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Greenville, SC, US USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>AWS, ECS, IAM, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cb4fd37f5d5683cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Blue Learning</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Lewisville, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, ETL, ELT, dbt, Tableau, Airflow</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1e8db13fab29835e</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Shopify Architect</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Docker</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc5601c059bd73a</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>WFP Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Git</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=644f70485107abbe</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>BI Developer</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>GCON Inc</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau, Airflow</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d9b57204f314618a</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-20.xlsx
+++ b/results/job_matches_2026-06-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,130 +538,130 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr. Associate, Site Reliability Engineering</t>
+          <t>Software Engineer III - AWS Glue / Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, API Gateway, ECS, IAM, RDS, Azure, Databricks</t>
+          <t>AWS, Glue, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d58654d97d98c4a</t>
+          <t>https://www.indeed.com/viewjob?jk=4944b59a58404b8f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS Glue / Data Engineer</t>
+          <t>Data Engineer- Full Time Opportunity, NOT C2C</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Codoxo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, S3, IAM, RDS, Spark, PySpark, Scala, PostgreSQL, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4944b59a58404b8f</t>
+          <t>https://www.indeed.com/viewjob?jk=780ec295f6bacdf5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Full Stack Developer React/ Java/ Python</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Middletown, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, API Gateway, RDS, Oracle, MySQL, DynamoDB, Splunk</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2637106dd2c7c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=d29d621da3e9a4ef</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer- Full Time Opportunity, NOT C2C</t>
+          <t>Sr. Feature Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Codoxo</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Spark, PySpark, Scala, PostgreSQL, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=780ec295f6bacdf5</t>
+          <t>https://www.indeed.com/viewjob?jk=b8442abf91777c1a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Full Stack Developer React/ Java/ Python</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Middletown, NJ, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,19 +706,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d29d621da3e9a4ef</t>
+          <t>https://www.indeed.com/viewjob?jk=6c2d8e205af354cd</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Feature Engineer</t>
+          <t>Senior Snowflake Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -727,38 +727,38 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8442abf91777c1a</t>
+          <t>https://www.indeed.com/viewjob?jk=cf016976f76e7f0a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Fresh Food QA Technician</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>7-Eleven</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,102 +776,102 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c2d8e205af354cd</t>
+          <t>https://www.indeed.com/viewjob?jk=4195bab3d9303fad</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Snowflake Engineer</t>
+          <t>Software Production Support Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>IntelliLink Technologies</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf016976f76e7f0a</t>
+          <t>https://www.indeed.com/viewjob?jk=416511572a3a38ba</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Fresh Food QA Technician</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7-Eleven</t>
+          <t>Arc Technologies Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, RDS, Azure, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4195bab3d9303fad</t>
+          <t>https://www.indeed.com/viewjob?jk=af690b2327755c54</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Production Support Engineer</t>
+          <t>Jr. Feature Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IntelliLink Technologies</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins</t>
+          <t>Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=416511572a3a38ba</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3a9fd6adbb852f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Fabric Platform Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Arc Technologies Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af690b2327755c54</t>
+          <t>https://www.indeed.com/viewjob?jk=7b1831e001122e4d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Jr. Feature Engineer</t>
+          <t>Fabric Platform Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3a9fd6adbb852f</t>
+          <t>https://www.indeed.com/viewjob?jk=3c7b8660e24dfc38</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Fullstack Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,67 +986,67 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372d6a67c10b163b</t>
+          <t>https://www.indeed.com/viewjob?jk=e08b28ff2bdfcb80</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Fabric Platform Engineer</t>
+          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b1831e001122e4d</t>
+          <t>https://www.indeed.com/viewjob?jk=1d97244cd7329e73</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Fabric Platform Engineer</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>RAZR Marketing, Inc.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, PostgreSQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,59 +1056,59 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c7b8660e24dfc38</t>
+          <t>https://www.indeed.com/viewjob?jk=7fde30b21f3e7647</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr Fullstack Developer</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Molex</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Lisle, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Glue, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e08b28ff2bdfcb80</t>
+          <t>https://www.indeed.com/viewjob?jk=461471cb36992ab7</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
+          <t>Associate</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Hadoop, Hive, Spark, PySpark, Kafka, Snowflake, ETL, Splunk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d97244cd7329e73</t>
+          <t>https://www.indeed.com/viewjob?jk=54b42443ee3c4437</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>Data Engineer, Cat Digital Data &amp; AI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>RAZR Marketing, Inc.</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, PostgreSQL, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fde30b21f3e7647</t>
+          <t>https://www.indeed.com/viewjob?jk=826181dbe0e126ae</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>IT Data Solutions Developer - Intermediate</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Molex</t>
+          <t>Atrium Health</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lisle, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=461471cb36992ab7</t>
+          <t>https://www.indeed.com/viewjob?jk=9c5097ade3e79b6c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Associate</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Vasa Fitness</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, Spark, PySpark, Kafka, Snowflake, ETL, Splunk</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54b42443ee3c4437</t>
+          <t>https://www.indeed.com/viewjob?jk=5ee3a253ea4b50de</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer, Cat Digital Data &amp; AI</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, GitHub Actions</t>
+          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=826181dbe0e126ae</t>
+          <t>https://www.indeed.com/viewjob?jk=bc4bd1d0f1519ea1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Vasa Fitness</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
+          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ee3a253ea4b50de</t>
+          <t>https://www.indeed.com/viewjob?jk=cf3f2dbb3812e475</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc4bd1d0f1519ea1</t>
+          <t>https://www.indeed.com/viewjob?jk=eeb8ab90439d98b8</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf3f2dbb3812e475</t>
+          <t>https://www.indeed.com/viewjob?jk=ea6ecf773d8deb21</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Kearney, NE, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeb8ab90439d98b8</t>
+          <t>https://www.indeed.com/viewjob?jk=a1d8f5634d6f6d76</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Grand Island, NE, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea6ecf773d8deb21</t>
+          <t>https://www.indeed.com/viewjob?jk=2ccaa9de6cb6d799</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kearney, NE, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,67 +1476,67 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d8f5634d6f6d76</t>
+          <t>https://www.indeed.com/viewjob?jk=47d6b37f8d80d085</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
+          <t>Software Engineer III - Python/PySpark/AWS</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ALLO Communications</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Grand Island, NE, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ccaa9de6cb6d799</t>
+          <t>https://www.indeed.com/viewjob?jk=7758e2775271790b</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
+          <t>Senior Software Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ALLO Communications</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47d6b37f8d80d085</t>
+          <t>https://www.indeed.com/viewjob?jk=4c67eab5c67331a9</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>IT Data Solutions Developer - Intermediate</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Atrium Health</t>
+          <t>Attain Finance</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, ECS, IAM, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c5097ade3e79b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=cb4fd37f5d5683cc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer III - Python/PySpark/AWS</t>
+          <t>Shopify Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, S3, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7758e2775271790b</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc5601c059bd73a</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Hybrid</t>
+          <t>WFP Senior Data Scientist</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,155 +1641,15 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Git</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4c67eab5c67331a9</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Senior Site Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Attain Finance</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Greenville, SC, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>AWS, ECS, IAM, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cb4fd37f5d5683cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Blue Learning</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Lewisville, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, ETL, ELT, dbt, Tableau, Airflow</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1e8db13fab29835e</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Shopify Architect</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Docker</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc5601c059bd73a</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>WFP Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Git</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=644f70485107abbe</t>
         </is>
